--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA542"/>
+  <dimension ref="A1:AA545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -58668,6 +58668,333 @@
       <c r="Z542" s="2" t="inlineStr"/>
       <c r="AA542" s="2" t="inlineStr"/>
     </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G543" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="inlineStr"/>
+      <c r="K543" s="2" t="inlineStr"/>
+      <c r="L543" s="2" t="inlineStr"/>
+      <c r="M543" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N543" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O543" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P543" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q543" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U543" s="2" t="inlineStr"/>
+      <c r="V543" s="2" t="inlineStr"/>
+      <c r="W543" s="2" t="inlineStr">
+        <is>
+          <t>António Paulo</t>
+        </is>
+      </c>
+      <c r="X543" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y543" s="2" t="inlineStr"/>
+      <c r="Z543" s="2" t="inlineStr"/>
+      <c r="AA543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-paulo-janes-da-costa-02b25169/</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D544" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E544" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F544" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G544" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="inlineStr"/>
+      <c r="K544" s="2" t="inlineStr"/>
+      <c r="L544" s="2" t="inlineStr"/>
+      <c r="M544" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N544" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O544" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P544" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q544" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U544" s="2" t="inlineStr"/>
+      <c r="V544" s="2" t="inlineStr"/>
+      <c r="W544" s="2" t="inlineStr">
+        <is>
+          <t>Rui Fontes Santos</t>
+        </is>
+      </c>
+      <c r="X544" s="2" t="inlineStr">
+        <is>
+          <t>Director of Corporate Procurement</t>
+        </is>
+      </c>
+      <c r="Y544" s="2" t="inlineStr"/>
+      <c r="Z544" s="2" t="inlineStr"/>
+      <c r="AA544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-fontes-santos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D545" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E545" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F545" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G545" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="inlineStr"/>
+      <c r="K545" s="2" t="inlineStr"/>
+      <c r="L545" s="2" t="inlineStr"/>
+      <c r="M545" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N545" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O545" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P545" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q545" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U545" s="2" t="inlineStr"/>
+      <c r="V545" s="2" t="inlineStr"/>
+      <c r="W545" s="2" t="inlineStr">
+        <is>
+          <t>João Nuno</t>
+        </is>
+      </c>
+      <c r="X545" s="2" t="inlineStr">
+        <is>
+          <t>Senior Logistics Specialist</t>
+        </is>
+      </c>
+      <c r="Y545" s="2" t="inlineStr"/>
+      <c r="Z545" s="2" t="inlineStr"/>
+      <c r="AA545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-nuno-perestrelo-aa3809ba/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA545"/>
+  <dimension ref="A1:AA548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -58995,6 +58995,333 @@
         </is>
       </c>
     </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D546" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E546" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F546" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G546" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="inlineStr"/>
+      <c r="K546" s="2" t="inlineStr"/>
+      <c r="L546" s="2" t="inlineStr"/>
+      <c r="M546" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N546" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O546" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P546" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q546" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U546" s="2" t="inlineStr"/>
+      <c r="V546" s="2" t="inlineStr"/>
+      <c r="W546" s="2" t="inlineStr">
+        <is>
+          <t>António Paulo</t>
+        </is>
+      </c>
+      <c r="X546" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y546" s="2" t="inlineStr"/>
+      <c r="Z546" s="2" t="inlineStr"/>
+      <c r="AA546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-paulo-janes-da-costa-02b25169/</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D547" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E547" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F547" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G547" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="inlineStr"/>
+      <c r="K547" s="2" t="inlineStr"/>
+      <c r="L547" s="2" t="inlineStr"/>
+      <c r="M547" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N547" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O547" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P547" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q547" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U547" s="2" t="inlineStr"/>
+      <c r="V547" s="2" t="inlineStr"/>
+      <c r="W547" s="2" t="inlineStr">
+        <is>
+          <t>Rui Fontes Santos</t>
+        </is>
+      </c>
+      <c r="X547" s="2" t="inlineStr">
+        <is>
+          <t>Director of Corporate Procurement</t>
+        </is>
+      </c>
+      <c r="Y547" s="2" t="inlineStr"/>
+      <c r="Z547" s="2" t="inlineStr"/>
+      <c r="AA547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-fontes-santos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D548" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E548" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F548" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G548" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="inlineStr"/>
+      <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="2" t="inlineStr"/>
+      <c r="M548" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N548" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O548" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P548" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q548" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U548" s="2" t="inlineStr"/>
+      <c r="V548" s="2" t="inlineStr"/>
+      <c r="W548" s="2" t="inlineStr">
+        <is>
+          <t>João Nuno</t>
+        </is>
+      </c>
+      <c r="X548" s="2" t="inlineStr">
+        <is>
+          <t>Senior Logistics Specialist</t>
+        </is>
+      </c>
+      <c r="Y548" s="2" t="inlineStr"/>
+      <c r="Z548" s="2" t="inlineStr"/>
+      <c r="AA548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-nuno-perestrelo-aa3809ba/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA548"/>
+  <dimension ref="A1:AA553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -59322,6 +59322,543 @@
         </is>
       </c>
     </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="D549" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E549" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="F549" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Choupelo 250</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>4400-088</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.theyeatman.com, https://www.the-yeatman-hotel.com</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="inlineStr"/>
+      <c r="K549" s="2" t="inlineStr"/>
+      <c r="L549" s="2" t="inlineStr"/>
+      <c r="M549" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N549" s="2" t="inlineStr">
+        <is>
+          <t>nuno.falcao@theyeatman.com</t>
+        </is>
+      </c>
+      <c r="O549" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 013 3100</t>
+        </is>
+      </c>
+      <c r="P549" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q549" s="2" t="inlineStr"/>
+      <c r="R549" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/the-yeatman/</t>
+        </is>
+      </c>
+      <c r="S549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheYeatmanPorto</t>
+        </is>
+      </c>
+      <c r="T549" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theyeatman</t>
+        </is>
+      </c>
+      <c r="U549" s="2" t="inlineStr"/>
+      <c r="V549" s="2" t="inlineStr"/>
+      <c r="W549" s="2" t="inlineStr">
+        <is>
+          <t>Elisabete Fernandes</t>
+        </is>
+      </c>
+      <c r="X549" s="2" t="inlineStr">
+        <is>
+          <t>Wine Director</t>
+        </is>
+      </c>
+      <c r="Y549" s="2" t="inlineStr"/>
+      <c r="Z549" s="2" t="inlineStr"/>
+      <c r="AA549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elisabete-fernandes-a88b14224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="D550" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E550" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="F550" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Choupelo 250</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>4400-088</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.theyeatman.com, https://www.the-yeatman-hotel.com</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="2" t="inlineStr"/>
+      <c r="M550" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N550" s="2" t="inlineStr">
+        <is>
+          <t>nuno.falcao@theyeatman.com</t>
+        </is>
+      </c>
+      <c r="O550" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 013 3100</t>
+        </is>
+      </c>
+      <c r="P550" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q550" s="2" t="inlineStr"/>
+      <c r="R550" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/the-yeatman/</t>
+        </is>
+      </c>
+      <c r="S550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheYeatmanPorto</t>
+        </is>
+      </c>
+      <c r="T550" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theyeatman</t>
+        </is>
+      </c>
+      <c r="U550" s="2" t="inlineStr"/>
+      <c r="V550" s="2" t="inlineStr"/>
+      <c r="W550" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Falcão</t>
+        </is>
+      </c>
+      <c r="X550" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y550" s="2" t="inlineStr"/>
+      <c r="Z550" s="2" t="inlineStr"/>
+      <c r="AA550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-falc%C3%A3o-4918b722</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D551" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E551" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F551" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G551" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="inlineStr"/>
+      <c r="K551" s="2" t="inlineStr"/>
+      <c r="L551" s="2" t="inlineStr"/>
+      <c r="M551" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N551" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O551" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P551" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q551" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U551" s="2" t="inlineStr"/>
+      <c r="V551" s="2" t="inlineStr"/>
+      <c r="W551" s="2" t="inlineStr">
+        <is>
+          <t>António Paulo</t>
+        </is>
+      </c>
+      <c r="X551" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y551" s="2" t="inlineStr"/>
+      <c r="Z551" s="2" t="inlineStr"/>
+      <c r="AA551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-paulo-janes-da-costa-02b25169/</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D552" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E552" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F552" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G552" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr"/>
+      <c r="L552" s="2" t="inlineStr"/>
+      <c r="M552" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N552" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O552" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P552" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q552" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U552" s="2" t="inlineStr"/>
+      <c r="V552" s="2" t="inlineStr"/>
+      <c r="W552" s="2" t="inlineStr">
+        <is>
+          <t>Rui Fontes Santos</t>
+        </is>
+      </c>
+      <c r="X552" s="2" t="inlineStr">
+        <is>
+          <t>Director of Corporate Procurement</t>
+        </is>
+      </c>
+      <c r="Y552" s="2" t="inlineStr"/>
+      <c r="Z552" s="2" t="inlineStr"/>
+      <c r="AA552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-fontes-santos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G553" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="inlineStr"/>
+      <c r="K553" s="2" t="inlineStr"/>
+      <c r="L553" s="2" t="inlineStr"/>
+      <c r="M553" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N553" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O553" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P553" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q553" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U553" s="2" t="inlineStr"/>
+      <c r="V553" s="2" t="inlineStr"/>
+      <c r="W553" s="2" t="inlineStr">
+        <is>
+          <t>João Nuno</t>
+        </is>
+      </c>
+      <c r="X553" s="2" t="inlineStr">
+        <is>
+          <t>Senior Logistics Specialist</t>
+        </is>
+      </c>
+      <c r="Y553" s="2" t="inlineStr"/>
+      <c r="Z553" s="2" t="inlineStr"/>
+      <c r="AA553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-nuno-perestrelo-aa3809ba/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA553"/>
+  <dimension ref="A1:AA558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -59859,6 +59859,543 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="D554" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E554" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="F554" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G554" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Choupelo 250</t>
+        </is>
+      </c>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>4400-088</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.theyeatman.com, https://www.the-yeatman-hotel.com</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr"/>
+      <c r="L554" s="2" t="inlineStr"/>
+      <c r="M554" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N554" s="2" t="inlineStr">
+        <is>
+          <t>nuno.falcao@theyeatman.com</t>
+        </is>
+      </c>
+      <c r="O554" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 013 3100</t>
+        </is>
+      </c>
+      <c r="P554" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q554" s="2" t="inlineStr"/>
+      <c r="R554" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/the-yeatman/</t>
+        </is>
+      </c>
+      <c r="S554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheYeatmanPorto</t>
+        </is>
+      </c>
+      <c r="T554" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theyeatman</t>
+        </is>
+      </c>
+      <c r="U554" s="2" t="inlineStr"/>
+      <c r="V554" s="2" t="inlineStr"/>
+      <c r="W554" s="2" t="inlineStr">
+        <is>
+          <t>Elisabete Fernandes</t>
+        </is>
+      </c>
+      <c r="X554" s="2" t="inlineStr">
+        <is>
+          <t>Wine Director</t>
+        </is>
+      </c>
+      <c r="Y554" s="2" t="inlineStr"/>
+      <c r="Z554" s="2" t="inlineStr"/>
+      <c r="AA554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elisabete-fernandes-a88b14224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>The Yeatman Wine Club</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="D555" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E555" s="2" t="inlineStr">
+        <is>
+          <t>Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="F555" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="G555" s="2" t="inlineStr">
+        <is>
+          <t>Rua Do Choupelo 250</t>
+        </is>
+      </c>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>4400-088</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr">
+        <is>
+          <t>https://shop.theyeatman.com, https://www.the-yeatman-hotel.com</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="inlineStr"/>
+      <c r="K555" s="2" t="inlineStr"/>
+      <c r="L555" s="2" t="inlineStr"/>
+      <c r="M555" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N555" s="2" t="inlineStr">
+        <is>
+          <t>nuno.falcao@theyeatman.com</t>
+        </is>
+      </c>
+      <c r="O555" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 013 3100</t>
+        </is>
+      </c>
+      <c r="P555" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q555" s="2" t="inlineStr"/>
+      <c r="R555" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/company/the-yeatman/</t>
+        </is>
+      </c>
+      <c r="S555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/TheYeatmanPorto</t>
+        </is>
+      </c>
+      <c r="T555" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/theyeatman</t>
+        </is>
+      </c>
+      <c r="U555" s="2" t="inlineStr"/>
+      <c r="V555" s="2" t="inlineStr"/>
+      <c r="W555" s="2" t="inlineStr">
+        <is>
+          <t>Nuno Falcão</t>
+        </is>
+      </c>
+      <c r="X555" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y555" s="2" t="inlineStr"/>
+      <c r="Z555" s="2" t="inlineStr"/>
+      <c r="AA555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nuno-falc%C3%A3o-4918b722</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D556" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E556" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F556" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G556" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr"/>
+      <c r="L556" s="2" t="inlineStr"/>
+      <c r="M556" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N556" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O556" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P556" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q556" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U556" s="2" t="inlineStr"/>
+      <c r="V556" s="2" t="inlineStr"/>
+      <c r="W556" s="2" t="inlineStr">
+        <is>
+          <t>António Paulo</t>
+        </is>
+      </c>
+      <c r="X556" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y556" s="2" t="inlineStr"/>
+      <c r="Z556" s="2" t="inlineStr"/>
+      <c r="AA556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ant%C3%B3nio-paulo-janes-da-costa-02b25169/</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D557" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E557" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F557" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G557" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="inlineStr"/>
+      <c r="K557" s="2" t="inlineStr"/>
+      <c r="L557" s="2" t="inlineStr"/>
+      <c r="M557" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N557" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O557" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P557" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q557" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U557" s="2" t="inlineStr"/>
+      <c r="V557" s="2" t="inlineStr"/>
+      <c r="W557" s="2" t="inlineStr">
+        <is>
+          <t>Rui Fontes Santos</t>
+        </is>
+      </c>
+      <c r="X557" s="2" t="inlineStr">
+        <is>
+          <t>Director of Corporate Procurement</t>
+        </is>
+      </c>
+      <c r="Y557" s="2" t="inlineStr"/>
+      <c r="Z557" s="2" t="inlineStr"/>
+      <c r="AA557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rui-fontes-santos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>Portspar Retail, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>49607</t>
+        </is>
+      </c>
+      <c r="D558" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E558" s="2" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F558" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Campanhã</t>
+        </is>
+      </c>
+      <c r="G558" s="2" t="inlineStr">
+        <is>
+          <t>365 Rua do Cerco do Porto</t>
+        </is>
+      </c>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>4300-119</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr">
+        <is>
+          <t>https://spar.pt</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr"/>
+      <c r="L558" s="2" t="inlineStr"/>
+      <c r="M558" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N558" s="2" t="inlineStr">
+        <is>
+          <t>antonio.costa@spar.pt</t>
+        </is>
+      </c>
+      <c r="O558" s="2" t="inlineStr">
+        <is>
+          <t>+351 22 615 6400</t>
+        </is>
+      </c>
+      <c r="P558" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q558" s="2" t="inlineStr">
+        <is>
+          <t>506175812</t>
+        </is>
+      </c>
+      <c r="R558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spar-portugal/</t>
+        </is>
+      </c>
+      <c r="S558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sparportugal/</t>
+        </is>
+      </c>
+      <c r="T558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sparportugal</t>
+        </is>
+      </c>
+      <c r="U558" s="2" t="inlineStr"/>
+      <c r="V558" s="2" t="inlineStr"/>
+      <c r="W558" s="2" t="inlineStr">
+        <is>
+          <t>João Nuno</t>
+        </is>
+      </c>
+      <c r="X558" s="2" t="inlineStr">
+        <is>
+          <t>Senior Logistics Specialist</t>
+        </is>
+      </c>
+      <c r="Y558" s="2" t="inlineStr"/>
+      <c r="Z558" s="2" t="inlineStr"/>
+      <c r="AA558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-nuno-perestrelo-aa3809ba/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA558"/>
+  <dimension ref="A1:AA559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -60396,6 +60396,99 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>Mascote Ilha Amarela, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>Mascote Ilha Amarela, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>145606</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>Vila do Porto</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>Açores</t>
+        </is>
+      </c>
+      <c r="G559" s="2" t="inlineStr">
+        <is>
+          <t>23 Rua Teófilo Braga</t>
+        </is>
+      </c>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>9580-535</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr">
+        <is>
+          <t>https://mascotewine.pt</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="inlineStr"/>
+      <c r="K559" s="2" t="inlineStr"/>
+      <c r="L559" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M559" s="2" t="inlineStr"/>
+      <c r="N559" s="2" t="inlineStr">
+        <is>
+          <t>mascotewine@sapo.pt</t>
+        </is>
+      </c>
+      <c r="O559" s="2" t="inlineStr"/>
+      <c r="P559" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q559" s="2" t="inlineStr">
+        <is>
+          <t>515903612</t>
+        </is>
+      </c>
+      <c r="R559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mascote-wine</t>
+        </is>
+      </c>
+      <c r="S559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WineMascote</t>
+        </is>
+      </c>
+      <c r="T559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mascotewine</t>
+        </is>
+      </c>
+      <c r="U559" s="2" t="inlineStr"/>
+      <c r="V559" s="2" t="inlineStr"/>
+      <c r="W559" s="2" t="inlineStr"/>
+      <c r="X559" s="2" t="inlineStr"/>
+      <c r="Y559" s="2" t="inlineStr"/>
+      <c r="Z559" s="2" t="inlineStr"/>
+      <c r="AA559" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA559"/>
+  <dimension ref="A1:AA567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -60489,6 +60489,722 @@
       <c r="Z559" s="2" t="inlineStr"/>
       <c r="AA559" s="2" t="inlineStr"/>
     </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>Vinhos E Sabores Lda</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>Vinhos E Sabores Lda</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>105818</t>
+        </is>
+      </c>
+      <c r="D560" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E560" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="F560" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G560" s="2" t="inlineStr">
+        <is>
+          <t>6A Rua Carlos Mayer</t>
+        </is>
+      </c>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>1700-102</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.portovintage.com</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr"/>
+      <c r="L560" s="2" t="inlineStr"/>
+      <c r="M560" s="2" t="inlineStr"/>
+      <c r="N560" s="2" t="inlineStr">
+        <is>
+          <t>bonjour@portovintage.com</t>
+        </is>
+      </c>
+      <c r="O560" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 397 6408</t>
+        </is>
+      </c>
+      <c r="P560" s="2" t="inlineStr"/>
+      <c r="Q560" s="2" t="inlineStr"/>
+      <c r="R560" s="2" t="inlineStr"/>
+      <c r="S560" s="2" t="inlineStr"/>
+      <c r="T560" s="2" t="inlineStr"/>
+      <c r="U560" s="2" t="inlineStr"/>
+      <c r="V560" s="2" t="inlineStr"/>
+      <c r="W560" s="2" t="inlineStr">
+        <is>
+          <t>Sylvain Favard</t>
+        </is>
+      </c>
+      <c r="X560" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y560" s="2" t="inlineStr"/>
+      <c r="Z560" s="2" t="inlineStr"/>
+      <c r="AA560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sylvain-favard-b4679855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>Wine Hunters, Lda</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>Wine Hunters, Lda</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>116124</t>
+        </is>
+      </c>
+      <c r="D561" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E561" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="F561" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G561" s="2" t="inlineStr">
+        <is>
+          <t>70a Rua Pascoal de Melo</t>
+        </is>
+      </c>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>1000-237</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winehunters.pt</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="inlineStr"/>
+      <c r="K561" s="2" t="inlineStr"/>
+      <c r="L561" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M561" s="2" t="inlineStr"/>
+      <c r="N561" s="2" t="inlineStr">
+        <is>
+          <t>info@winehunters.pt</t>
+        </is>
+      </c>
+      <c r="O561" s="2" t="inlineStr">
+        <is>
+          <t>+351 21 581 2333</t>
+        </is>
+      </c>
+      <c r="P561" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q561" s="2" t="inlineStr">
+        <is>
+          <t>514920777</t>
+        </is>
+      </c>
+      <c r="R561" s="2" t="inlineStr"/>
+      <c r="S561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winehunterstaberna/</t>
+        </is>
+      </c>
+      <c r="T561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winehunterstaberna/</t>
+        </is>
+      </c>
+      <c r="U561" s="2" t="inlineStr"/>
+      <c r="V561" s="2" t="inlineStr"/>
+      <c r="W561" s="2" t="inlineStr">
+        <is>
+          <t>João Paulo Santos</t>
+        </is>
+      </c>
+      <c r="X561" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y561" s="2" t="inlineStr"/>
+      <c r="Z561" s="2" t="inlineStr"/>
+      <c r="AA561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jo%C3%A3o-paulo-santos-738b1916b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>Garrafaria - Comércio De Vinhos, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>Garrafaria - Comércio De Vinhos, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>97166</t>
+        </is>
+      </c>
+      <c r="D562" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E562" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="F562" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G562" s="2" t="inlineStr">
+        <is>
+          <t>44 Rua Dom Pedro V</t>
+        </is>
+      </c>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>1250-094</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiraimperial.com</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="inlineStr"/>
+      <c r="K562" s="2" t="inlineStr"/>
+      <c r="L562" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M562" s="2" t="inlineStr"/>
+      <c r="N562" s="2" t="inlineStr">
+        <is>
+          <t>store@garrafeiraimperial.com</t>
+        </is>
+      </c>
+      <c r="O562" s="2" t="inlineStr"/>
+      <c r="P562" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q562" s="2" t="inlineStr">
+        <is>
+          <t>514163062</t>
+        </is>
+      </c>
+      <c r="R562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garrafeira-imperial/</t>
+        </is>
+      </c>
+      <c r="S562" s="2" t="inlineStr"/>
+      <c r="T562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiraimperial/</t>
+        </is>
+      </c>
+      <c r="U562" s="2" t="inlineStr"/>
+      <c r="V562" s="2" t="inlineStr"/>
+      <c r="W562" s="2" t="inlineStr">
+        <is>
+          <t>Gilcier Fernandes</t>
+        </is>
+      </c>
+      <c r="X562" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y562" s="2" t="inlineStr"/>
+      <c r="Z562" s="2" t="inlineStr"/>
+      <c r="AA562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gilcier-fernandes-257b3b57/</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Garrafaria - Comércio De Vinhos, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>Garrafaria - Comércio De Vinhos, Unipessoal, Lda</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>97166</t>
+        </is>
+      </c>
+      <c r="D563" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E563" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="F563" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G563" s="2" t="inlineStr">
+        <is>
+          <t>44 Rua Dom Pedro V</t>
+        </is>
+      </c>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>1250-094</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiraimperial.com</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="inlineStr"/>
+      <c r="K563" s="2" t="inlineStr"/>
+      <c r="L563" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M563" s="2" t="inlineStr"/>
+      <c r="N563" s="2" t="inlineStr">
+        <is>
+          <t>store@garrafeiraimperial.com</t>
+        </is>
+      </c>
+      <c r="O563" s="2" t="inlineStr"/>
+      <c r="P563" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q563" s="2" t="inlineStr">
+        <is>
+          <t>514163062</t>
+        </is>
+      </c>
+      <c r="R563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/garrafeira-imperial/</t>
+        </is>
+      </c>
+      <c r="S563" s="2" t="inlineStr"/>
+      <c r="T563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiraimperial/</t>
+        </is>
+      </c>
+      <c r="U563" s="2" t="inlineStr"/>
+      <c r="V563" s="2" t="inlineStr"/>
+      <c r="W563" s="2" t="inlineStr">
+        <is>
+          <t>Vítor Hipolito</t>
+        </is>
+      </c>
+      <c r="X563" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y563" s="2" t="inlineStr"/>
+      <c r="Z563" s="2" t="inlineStr"/>
+      <c r="AA563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/v%C3%ADtor-hipolito-18975647/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>Contágio Boa Ideia, Lda</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>Contágio Boa Ideia, Lda</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>115423</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>Cacia</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>Aveiro, Aveiro</t>
+        </is>
+      </c>
+      <c r="G564" s="2" t="inlineStr">
+        <is>
+          <t>235 Rua da Paz</t>
+        </is>
+      </c>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>3800-587</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr">
+        <is>
+          <t>https://contagiovinhos.pt</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr"/>
+      <c r="L564" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M564" s="2" t="inlineStr"/>
+      <c r="N564" s="2" t="inlineStr">
+        <is>
+          <t>contagiovinhos@gmail.com</t>
+        </is>
+      </c>
+      <c r="O564" s="2" t="inlineStr">
+        <is>
+          <t>+351 234 916 025</t>
+        </is>
+      </c>
+      <c r="P564" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q564" s="2" t="inlineStr">
+        <is>
+          <t>509920632</t>
+        </is>
+      </c>
+      <c r="R564" s="2" t="inlineStr"/>
+      <c r="S564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100088125892457</t>
+        </is>
+      </c>
+      <c r="T564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiracontagio/</t>
+        </is>
+      </c>
+      <c r="U564" s="2" t="inlineStr"/>
+      <c r="V564" s="2" t="inlineStr"/>
+      <c r="W564" s="2" t="inlineStr"/>
+      <c r="X564" s="2" t="inlineStr"/>
+      <c r="Y564" s="2" t="inlineStr"/>
+      <c r="Z564" s="2" t="inlineStr"/>
+      <c r="AA564" s="2" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>Essence Drinks</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>Essence Drinks</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>96725</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E565" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="F565" s="2" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="G565" s="2" t="inlineStr">
+        <is>
+          <t>Rua Nova de Sta Cruz nº37 A</t>
+        </is>
+      </c>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>4710-409</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr">
+        <is>
+          <t>https://essencedrinks.com</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="inlineStr"/>
+      <c r="K565" s="2" t="inlineStr"/>
+      <c r="L565" s="2" t="inlineStr"/>
+      <c r="M565" s="2" t="inlineStr"/>
+      <c r="N565" s="2" t="inlineStr">
+        <is>
+          <t>geral@essencedrinks.com</t>
+        </is>
+      </c>
+      <c r="O565" s="2" t="inlineStr"/>
+      <c r="P565" s="2" t="inlineStr"/>
+      <c r="Q565" s="2" t="inlineStr"/>
+      <c r="R565" s="2" t="inlineStr"/>
+      <c r="S565" s="2" t="inlineStr"/>
+      <c r="T565" s="2" t="inlineStr"/>
+      <c r="U565" s="2" t="inlineStr"/>
+      <c r="V565" s="2" t="inlineStr"/>
+      <c r="W565" s="2" t="inlineStr"/>
+      <c r="X565" s="2" t="inlineStr"/>
+      <c r="Y565" s="2" t="inlineStr"/>
+      <c r="Z565" s="2" t="inlineStr"/>
+      <c r="AA565" s="2" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>Vinogrande</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>Vinogrande</t>
+        </is>
+      </c>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>108241</t>
+        </is>
+      </c>
+      <c r="D566" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E566" s="2" t="inlineStr">
+        <is>
+          <t>Moledo</t>
+        </is>
+      </c>
+      <c r="F566" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo, Caminha, União das freguesias de Moledo e Cristelo</t>
+        </is>
+      </c>
+      <c r="G566" s="2" t="inlineStr">
+        <is>
+          <t>393 Avenida Santana</t>
+        </is>
+      </c>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>4910-235</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr">
+        <is>
+          <t>https://vinogrande.pt, https://www.garrafeiravinogrande.com</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
+      <c r="L566" s="2" t="inlineStr"/>
+      <c r="M566" s="2" t="inlineStr"/>
+      <c r="N566" s="2" t="inlineStr">
+        <is>
+          <t>contacto@vinogrande.pt</t>
+        </is>
+      </c>
+      <c r="O566" s="2" t="inlineStr">
+        <is>
+          <t>+351 258 723 044</t>
+        </is>
+      </c>
+      <c r="P566" s="2" t="inlineStr"/>
+      <c r="Q566" s="2" t="inlineStr"/>
+      <c r="R566" s="2" t="inlineStr"/>
+      <c r="S566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinogrande.pt</t>
+        </is>
+      </c>
+      <c r="T566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeiravinogrande</t>
+        </is>
+      </c>
+      <c r="U566" s="2" t="inlineStr"/>
+      <c r="V566" s="2" t="inlineStr"/>
+      <c r="W566" s="2" t="inlineStr">
+        <is>
+          <t>João Paulo</t>
+        </is>
+      </c>
+      <c r="X566" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y566" s="2" t="inlineStr"/>
+      <c r="Z566" s="2" t="inlineStr"/>
+      <c r="AA566" s="2" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Ideal</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>Garrafeira Ideal</t>
+        </is>
+      </c>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>11357</t>
+        </is>
+      </c>
+      <c r="D567" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E567" s="2" t="inlineStr">
+        <is>
+          <t>Caranguejeira</t>
+        </is>
+      </c>
+      <c r="F567" s="2" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="G567" s="2" t="inlineStr">
+        <is>
+          <t>5 Rua do Lagar</t>
+        </is>
+      </c>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>2420-166</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr">
+        <is>
+          <t>https://garrafeiraideal.com</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="inlineStr"/>
+      <c r="K567" s="2" t="inlineStr"/>
+      <c r="L567" s="2" t="inlineStr"/>
+      <c r="M567" s="2" t="inlineStr"/>
+      <c r="N567" s="2" t="inlineStr">
+        <is>
+          <t>garrafeiraideal@gmail.com</t>
+        </is>
+      </c>
+      <c r="O567" s="2" t="inlineStr">
+        <is>
+          <t>+351 244 734 639</t>
+        </is>
+      </c>
+      <c r="P567" s="2" t="inlineStr"/>
+      <c r="Q567" s="2" t="inlineStr"/>
+      <c r="R567" s="2" t="inlineStr"/>
+      <c r="S567" s="2" t="inlineStr"/>
+      <c r="T567" s="2" t="inlineStr"/>
+      <c r="U567" s="2" t="inlineStr"/>
+      <c r="V567" s="2" t="inlineStr"/>
+      <c r="W567" s="2" t="inlineStr"/>
+      <c r="X567" s="2" t="inlineStr"/>
+      <c r="Y567" s="2" t="inlineStr"/>
+      <c r="Z567" s="2" t="inlineStr"/>
+      <c r="AA567" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA567"/>
+  <dimension ref="A1:AA569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61205,6 +61205,224 @@
       <c r="Z567" s="2" t="inlineStr"/>
       <c r="AA567" s="2" t="inlineStr"/>
     </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>Fgp - Fonseca, Garcia &amp; Prazeres, Lda</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>Fgp - Fonseca, Garcia &amp; Prazeres, Lda</t>
+        </is>
+      </c>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>11355</t>
+        </is>
+      </c>
+      <c r="D568" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E568" s="2" t="inlineStr">
+        <is>
+          <t>Bombarral</t>
+        </is>
+      </c>
+      <c r="F568" s="2" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="G568" s="2" t="inlineStr">
+        <is>
+          <t>Rua Gil Eanes nº 33</t>
+        </is>
+      </c>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>2540-172</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fgp.pt</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
+      <c r="L568" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="inlineStr"/>
+      <c r="N568" s="2" t="inlineStr">
+        <is>
+          <t>geral@fgp.pt</t>
+        </is>
+      </c>
+      <c r="O568" s="2" t="inlineStr">
+        <is>
+          <t>+351 262 287 200</t>
+        </is>
+      </c>
+      <c r="P568" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q568" s="2" t="inlineStr">
+        <is>
+          <t>502284277</t>
+        </is>
+      </c>
+      <c r="R568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fgp-distribuidores-bebidas/</t>
+        </is>
+      </c>
+      <c r="S568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeirafgp/</t>
+        </is>
+      </c>
+      <c r="T568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeirafgp</t>
+        </is>
+      </c>
+      <c r="U568" s="2" t="inlineStr"/>
+      <c r="V568" s="2" t="inlineStr"/>
+      <c r="W568" s="2" t="inlineStr">
+        <is>
+          <t>Filipe Fonseca</t>
+        </is>
+      </c>
+      <c r="X568" s="2" t="inlineStr">
+        <is>
+          <t>Director General</t>
+        </is>
+      </c>
+      <c r="Y568" s="2" t="inlineStr"/>
+      <c r="Z568" s="2" t="inlineStr"/>
+      <c r="AA568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/filipe-fonseca-64258320/</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>Fgp - Fonseca, Garcia &amp; Prazeres, Lda</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>Fgp - Fonseca, Garcia &amp; Prazeres, Lda</t>
+        </is>
+      </c>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>11355</t>
+        </is>
+      </c>
+      <c r="D569" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E569" s="2" t="inlineStr">
+        <is>
+          <t>Bombarral</t>
+        </is>
+      </c>
+      <c r="F569" s="2" t="inlineStr">
+        <is>
+          <t>Leiria</t>
+        </is>
+      </c>
+      <c r="G569" s="2" t="inlineStr">
+        <is>
+          <t>Rua Gil Eanes nº 33</t>
+        </is>
+      </c>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>2540-172</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fgp.pt</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="inlineStr"/>
+      <c r="K569" s="2" t="inlineStr"/>
+      <c r="L569" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="inlineStr"/>
+      <c r="N569" s="2" t="inlineStr">
+        <is>
+          <t>geral@fgp.pt</t>
+        </is>
+      </c>
+      <c r="O569" s="2" t="inlineStr">
+        <is>
+          <t>+351 262 287 200</t>
+        </is>
+      </c>
+      <c r="P569" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="Q569" s="2" t="inlineStr">
+        <is>
+          <t>502284277</t>
+        </is>
+      </c>
+      <c r="R569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fgp-distribuidores-bebidas/</t>
+        </is>
+      </c>
+      <c r="S569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/garrafeirafgp/</t>
+        </is>
+      </c>
+      <c r="T569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/garrafeirafgp</t>
+        </is>
+      </c>
+      <c r="U569" s="2" t="inlineStr"/>
+      <c r="V569" s="2" t="inlineStr"/>
+      <c r="W569" s="2" t="inlineStr">
+        <is>
+          <t>Ilidio Antunes</t>
+        </is>
+      </c>
+      <c r="X569" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y569" s="2" t="inlineStr"/>
+      <c r="Z569" s="2" t="inlineStr"/>
+      <c r="AA569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilidio-antunes-5a00b861/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA569"/>
+  <dimension ref="A1:AA572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61423,6 +61423,325 @@
         </is>
       </c>
     </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D570" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E570" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F570" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G570" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
+      <c r="L570" s="2" t="inlineStr"/>
+      <c r="M570" s="2" t="inlineStr"/>
+      <c r="N570" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O570" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P570" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q570" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U570" s="2" t="inlineStr"/>
+      <c r="V570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W570" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Vieira</t>
+        </is>
+      </c>
+      <c r="X570" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y570" s="2" t="inlineStr"/>
+      <c r="Z570" s="2" t="inlineStr"/>
+      <c r="AA570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristina-vieira-61514655</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D571" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E571" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F571" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G571" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="inlineStr"/>
+      <c r="K571" s="2" t="inlineStr"/>
+      <c r="L571" s="2" t="inlineStr"/>
+      <c r="M571" s="2" t="inlineStr"/>
+      <c r="N571" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O571" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P571" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q571" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U571" s="2" t="inlineStr"/>
+      <c r="V571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W571" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Rocha</t>
+        </is>
+      </c>
+      <c r="X571" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y571" s="2" t="inlineStr"/>
+      <c r="Z571" s="2" t="inlineStr"/>
+      <c r="AA571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-rocha-6296b5113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="D572" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E572" s="2" t="inlineStr">
+        <is>
+          <t>Valença</t>
+        </is>
+      </c>
+      <c r="F572" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G572" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Tuido-gandra, S/n</t>
+        </is>
+      </c>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>4930-327</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.froiz.com, https://www.froiz.pt</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="2" t="inlineStr"/>
+      <c r="M572" s="2" t="inlineStr"/>
+      <c r="N572" s="2" t="inlineStr">
+        <is>
+          <t>info@froiz.pt</t>
+        </is>
+      </c>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>+351 251 825 870</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr"/>
+      <c r="Q572" s="2" t="inlineStr"/>
+      <c r="R572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-froiz-portugal/</t>
+        </is>
+      </c>
+      <c r="S572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosFroizPortugal/</t>
+        </is>
+      </c>
+      <c r="T572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercados_froiz_portugal</t>
+        </is>
+      </c>
+      <c r="U572" s="2" t="inlineStr"/>
+      <c r="V572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdwx7fZ8fZWZKTGlfczaSfg</t>
+        </is>
+      </c>
+      <c r="W572" s="2" t="inlineStr">
+        <is>
+          <t>Flora Sousa</t>
+        </is>
+      </c>
+      <c r="X572" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y572" s="2" t="inlineStr"/>
+      <c r="Z572" s="2" t="inlineStr"/>
+      <c r="AA572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/flora-sousa-047a74336/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA572"/>
+  <dimension ref="A1:AA575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -61742,6 +61742,325 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D573" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E573" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F573" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G573" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="inlineStr"/>
+      <c r="K573" s="2" t="inlineStr"/>
+      <c r="L573" s="2" t="inlineStr"/>
+      <c r="M573" s="2" t="inlineStr"/>
+      <c r="N573" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O573" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P573" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q573" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U573" s="2" t="inlineStr"/>
+      <c r="V573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W573" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Vieira</t>
+        </is>
+      </c>
+      <c r="X573" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y573" s="2" t="inlineStr"/>
+      <c r="Z573" s="2" t="inlineStr"/>
+      <c r="AA573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristina-vieira-61514655</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D574" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E574" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F574" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G574" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="inlineStr"/>
+      <c r="K574" s="2" t="inlineStr"/>
+      <c r="L574" s="2" t="inlineStr"/>
+      <c r="M574" s="2" t="inlineStr"/>
+      <c r="N574" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O574" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P574" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q574" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U574" s="2" t="inlineStr"/>
+      <c r="V574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W574" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Rocha</t>
+        </is>
+      </c>
+      <c r="X574" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y574" s="2" t="inlineStr"/>
+      <c r="Z574" s="2" t="inlineStr"/>
+      <c r="AA574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-rocha-6296b5113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="D575" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E575" s="2" t="inlineStr">
+        <is>
+          <t>Valença</t>
+        </is>
+      </c>
+      <c r="F575" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G575" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Tuido-gandra, S/n</t>
+        </is>
+      </c>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>4930-327</t>
+        </is>
+      </c>
+      <c r="I575" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.froiz.com, https://www.froiz.pt</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="inlineStr"/>
+      <c r="K575" s="2" t="inlineStr"/>
+      <c r="L575" s="2" t="inlineStr"/>
+      <c r="M575" s="2" t="inlineStr"/>
+      <c r="N575" s="2" t="inlineStr">
+        <is>
+          <t>info@froiz.pt</t>
+        </is>
+      </c>
+      <c r="O575" s="2" t="inlineStr">
+        <is>
+          <t>+351 251 825 870</t>
+        </is>
+      </c>
+      <c r="P575" s="2" t="inlineStr"/>
+      <c r="Q575" s="2" t="inlineStr"/>
+      <c r="R575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-froiz-portugal/</t>
+        </is>
+      </c>
+      <c r="S575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosFroizPortugal/</t>
+        </is>
+      </c>
+      <c r="T575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercados_froiz_portugal</t>
+        </is>
+      </c>
+      <c r="U575" s="2" t="inlineStr"/>
+      <c r="V575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdwx7fZ8fZWZKTGlfczaSfg</t>
+        </is>
+      </c>
+      <c r="W575" s="2" t="inlineStr">
+        <is>
+          <t>Flora Sousa</t>
+        </is>
+      </c>
+      <c r="X575" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y575" s="2" t="inlineStr"/>
+      <c r="Z575" s="2" t="inlineStr"/>
+      <c r="AA575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/flora-sousa-047a74336/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA575"/>
+  <dimension ref="A1:AA578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -62061,6 +62061,325 @@
         </is>
       </c>
     </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D576" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E576" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F576" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G576" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="2" t="inlineStr"/>
+      <c r="M576" s="2" t="inlineStr"/>
+      <c r="N576" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O576" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P576" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q576" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U576" s="2" t="inlineStr"/>
+      <c r="V576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W576" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Vieira</t>
+        </is>
+      </c>
+      <c r="X576" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y576" s="2" t="inlineStr"/>
+      <c r="Z576" s="2" t="inlineStr"/>
+      <c r="AA576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristina-vieira-61514655</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D577" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E577" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F577" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="inlineStr"/>
+      <c r="K577" s="2" t="inlineStr"/>
+      <c r="L577" s="2" t="inlineStr"/>
+      <c r="M577" s="2" t="inlineStr"/>
+      <c r="N577" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O577" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P577" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q577" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U577" s="2" t="inlineStr"/>
+      <c r="V577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W577" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Rocha</t>
+        </is>
+      </c>
+      <c r="X577" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y577" s="2" t="inlineStr"/>
+      <c r="Z577" s="2" t="inlineStr"/>
+      <c r="AA577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-rocha-6296b5113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="D578" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E578" s="2" t="inlineStr">
+        <is>
+          <t>Valença</t>
+        </is>
+      </c>
+      <c r="F578" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Tuido-gandra, S/n</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>4930-327</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.froiz.com, https://www.froiz.pt</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="2" t="inlineStr"/>
+      <c r="M578" s="2" t="inlineStr"/>
+      <c r="N578" s="2" t="inlineStr">
+        <is>
+          <t>info@froiz.pt</t>
+        </is>
+      </c>
+      <c r="O578" s="2" t="inlineStr">
+        <is>
+          <t>+351 251 825 870</t>
+        </is>
+      </c>
+      <c r="P578" s="2" t="inlineStr"/>
+      <c r="Q578" s="2" t="inlineStr"/>
+      <c r="R578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-froiz-portugal/</t>
+        </is>
+      </c>
+      <c r="S578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosFroizPortugal/</t>
+        </is>
+      </c>
+      <c r="T578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercados_froiz_portugal</t>
+        </is>
+      </c>
+      <c r="U578" s="2" t="inlineStr"/>
+      <c r="V578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdwx7fZ8fZWZKTGlfczaSfg</t>
+        </is>
+      </c>
+      <c r="W578" s="2" t="inlineStr">
+        <is>
+          <t>Flora Sousa</t>
+        </is>
+      </c>
+      <c r="X578" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y578" s="2" t="inlineStr"/>
+      <c r="Z578" s="2" t="inlineStr"/>
+      <c r="AA578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/flora-sousa-047a74336/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA578"/>
+  <dimension ref="A1:AA581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -62380,6 +62380,325 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D579" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E579" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F579" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G579" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="inlineStr"/>
+      <c r="K579" s="2" t="inlineStr"/>
+      <c r="L579" s="2" t="inlineStr"/>
+      <c r="M579" s="2" t="inlineStr"/>
+      <c r="N579" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O579" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P579" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q579" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U579" s="2" t="inlineStr"/>
+      <c r="V579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W579" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Vieira</t>
+        </is>
+      </c>
+      <c r="X579" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y579" s="2" t="inlineStr"/>
+      <c r="Z579" s="2" t="inlineStr"/>
+      <c r="AA579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristina-vieira-61514655</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D580" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E580" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F580" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G580" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
+      <c r="L580" s="2" t="inlineStr"/>
+      <c r="M580" s="2" t="inlineStr"/>
+      <c r="N580" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O580" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P580" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q580" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U580" s="2" t="inlineStr"/>
+      <c r="V580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W580" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Rocha</t>
+        </is>
+      </c>
+      <c r="X580" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y580" s="2" t="inlineStr"/>
+      <c r="Z580" s="2" t="inlineStr"/>
+      <c r="AA580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-rocha-6296b5113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="D581" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E581" s="2" t="inlineStr">
+        <is>
+          <t>Valença</t>
+        </is>
+      </c>
+      <c r="F581" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G581" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Tuido-gandra, S/n</t>
+        </is>
+      </c>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>4930-327</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.froiz.com, https://www.froiz.pt</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="inlineStr"/>
+      <c r="K581" s="2" t="inlineStr"/>
+      <c r="L581" s="2" t="inlineStr"/>
+      <c r="M581" s="2" t="inlineStr"/>
+      <c r="N581" s="2" t="inlineStr">
+        <is>
+          <t>info@froiz.pt</t>
+        </is>
+      </c>
+      <c r="O581" s="2" t="inlineStr">
+        <is>
+          <t>+351 251 825 870</t>
+        </is>
+      </c>
+      <c r="P581" s="2" t="inlineStr"/>
+      <c r="Q581" s="2" t="inlineStr"/>
+      <c r="R581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-froiz-portugal/</t>
+        </is>
+      </c>
+      <c r="S581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosFroizPortugal/</t>
+        </is>
+      </c>
+      <c r="T581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercados_froiz_portugal</t>
+        </is>
+      </c>
+      <c r="U581" s="2" t="inlineStr"/>
+      <c r="V581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdwx7fZ8fZWZKTGlfczaSfg</t>
+        </is>
+      </c>
+      <c r="W581" s="2" t="inlineStr">
+        <is>
+          <t>Flora Sousa</t>
+        </is>
+      </c>
+      <c r="X581" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y581" s="2" t="inlineStr"/>
+      <c r="Z581" s="2" t="inlineStr"/>
+      <c r="AA581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/flora-sousa-047a74336/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Portugal.xlsx
+++ b/BWI/bestwine_output/bestwine_Portugal.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA581"/>
+  <dimension ref="A1:AA584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -62699,6 +62699,325 @@
         </is>
       </c>
     </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D582" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E582" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F582" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G582" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
+      <c r="L582" s="2" t="inlineStr"/>
+      <c r="M582" s="2" t="inlineStr"/>
+      <c r="N582" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O582" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P582" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q582" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U582" s="2" t="inlineStr"/>
+      <c r="V582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W582" s="2" t="inlineStr">
+        <is>
+          <t>Cristina Vieira</t>
+        </is>
+      </c>
+      <c r="X582" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y582" s="2" t="inlineStr"/>
+      <c r="Z582" s="2" t="inlineStr"/>
+      <c r="AA582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/cristina-vieira-61514655</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>Recheio Cash &amp; Carry, S.a.</t>
+        </is>
+      </c>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>96961</t>
+        </is>
+      </c>
+      <c r="D583" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E583" s="2" t="inlineStr">
+        <is>
+          <t>Amadora</t>
+        </is>
+      </c>
+      <c r="F583" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="G583" s="2" t="inlineStr">
+        <is>
+          <t>7 Rua Actor António Silva</t>
+        </is>
+      </c>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.recheio.pt</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="inlineStr"/>
+      <c r="K583" s="2" t="inlineStr"/>
+      <c r="L583" s="2" t="inlineStr"/>
+      <c r="M583" s="2" t="inlineStr"/>
+      <c r="N583" s="2" t="inlineStr">
+        <is>
+          <t>cliente@recheio.pt</t>
+        </is>
+      </c>
+      <c r="O583" s="2" t="inlineStr">
+        <is>
+          <t>+351 800 203 131</t>
+        </is>
+      </c>
+      <c r="P583" s="2" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="Q583" s="2" t="inlineStr">
+        <is>
+          <t>500145415</t>
+        </is>
+      </c>
+      <c r="R583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recheiosa/</t>
+        </is>
+      </c>
+      <c r="S583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Recheio.pt/</t>
+        </is>
+      </c>
+      <c r="T583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/recheiopt/</t>
+        </is>
+      </c>
+      <c r="U583" s="2" t="inlineStr"/>
+      <c r="V583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@recheiopt</t>
+        </is>
+      </c>
+      <c r="W583" s="2" t="inlineStr">
+        <is>
+          <t>Cátia Rocha</t>
+        </is>
+      </c>
+      <c r="X583" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y583" s="2" t="inlineStr"/>
+      <c r="Z583" s="2" t="inlineStr"/>
+      <c r="AA583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/c%C3%A1tia-rocha-6296b5113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>Supermercados Froiz</t>
+        </is>
+      </c>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>97034</t>
+        </is>
+      </c>
+      <c r="D584" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="E584" s="2" t="inlineStr">
+        <is>
+          <t>Valença</t>
+        </is>
+      </c>
+      <c r="F584" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo</t>
+        </is>
+      </c>
+      <c r="G584" s="2" t="inlineStr">
+        <is>
+          <t>Estrada Tuido-gandra, S/n</t>
+        </is>
+      </c>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>4930-327</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr">
+        <is>
+          <t>https://loja.froiz.com, https://www.froiz.pt</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr"/>
+      <c r="L584" s="2" t="inlineStr"/>
+      <c r="M584" s="2" t="inlineStr"/>
+      <c r="N584" s="2" t="inlineStr">
+        <is>
+          <t>info@froiz.pt</t>
+        </is>
+      </c>
+      <c r="O584" s="2" t="inlineStr">
+        <is>
+          <t>+351 251 825 870</t>
+        </is>
+      </c>
+      <c r="P584" s="2" t="inlineStr"/>
+      <c r="Q584" s="2" t="inlineStr"/>
+      <c r="R584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/supermercados-froiz-portugal/</t>
+        </is>
+      </c>
+      <c r="S584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/SupermercadosFroizPortugal/</t>
+        </is>
+      </c>
+      <c r="T584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/supermercados_froiz_portugal</t>
+        </is>
+      </c>
+      <c r="U584" s="2" t="inlineStr"/>
+      <c r="V584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCdwx7fZ8fZWZKTGlfczaSfg</t>
+        </is>
+      </c>
+      <c r="W584" s="2" t="inlineStr">
+        <is>
+          <t>Flora Sousa</t>
+        </is>
+      </c>
+      <c r="X584" s="2" t="inlineStr">
+        <is>
+          <t>Store Manager</t>
+        </is>
+      </c>
+      <c r="Y584" s="2" t="inlineStr"/>
+      <c r="Z584" s="2" t="inlineStr"/>
+      <c r="AA584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/flora-sousa-047a74336/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
